--- a/agile_doc/hospital_ivr_agile_template.xlsx
+++ b/agile_doc/hospital_ivr_agile_template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="167">
   <si>
     <t>Numbers Sheet Name</t>
   </si>
@@ -181,12 +181,6 @@
     <t>Design IVR frontend UI</t>
   </si>
   <si>
-    <t>2026-02-01</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
     <t>UI Development</t>
   </si>
   <si>
@@ -202,12 +196,6 @@
     <t>Develop FastAPI IVR backend</t>
   </si>
   <si>
-    <t>2026-02-04</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
     <t>Backend API</t>
   </si>
   <si>
@@ -220,12 +208,6 @@
     <t>Lab report API</t>
   </si>
   <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
-  </si>
-  <si>
     <t>API Logic</t>
   </si>
   <si>
@@ -235,12 +217,6 @@
     <t>Billing enquiry logic</t>
   </si>
   <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
     <t>Billing Module</t>
   </si>
   <si>
@@ -253,12 +229,6 @@
     <t>Speech recognition integration</t>
   </si>
   <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
     <t>AI Integration</t>
   </si>
   <si>
@@ -271,12 +241,6 @@
     <t>Analytics endpoint</t>
   </si>
   <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
     <t>Analytics</t>
   </si>
   <si>
@@ -349,9 +313,6 @@
     <t>Continue Doing</t>
   </si>
   <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
     <t>Frontend &amp; Backend</t>
   </si>
   <si>
@@ -431,6 +392,138 @@
   </si>
   <si>
     <t>ü</t>
+  </si>
+  <si>
+    <t>sprint 4</t>
+  </si>
+  <si>
+    <t>QA &amp; Full Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Perform testing &amp; deploy application </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skipping test cases  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bug tracking </t>
+  </si>
+  <si>
+    <t>Fixed issues and deployed on Render</t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient ID not working with voice + keypad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicate voice input display </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deployment issues </t>
+  </si>
+  <si>
+    <t>Corrected start command and environment configuration</t>
+  </si>
+  <si>
+    <t>Synchronized conversation and menu states</t>
+  </si>
+  <si>
+    <t>Fixed frontend duplication in speech handling</t>
+  </si>
+  <si>
+    <t>US007</t>
+  </si>
+  <si>
+    <t>US008</t>
+  </si>
+  <si>
+    <t>US009</t>
+  </si>
+  <si>
+    <t>US010</t>
+  </si>
+  <si>
+    <t>US011</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>T8</t>
+  </si>
+  <si>
+    <t>T9</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit testing (API + modules)  </t>
+  </si>
+  <si>
+    <t>Integration testing (IVR flow)</t>
+  </si>
+  <si>
+    <t>Bug fixing &amp; optimization</t>
+  </si>
+  <si>
+    <t>Deployment on Render</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Final testing &amp; validation</t>
+  </si>
+  <si>
+    <t>29-02-2026</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>QA &amp; Developer Team</t>
+  </si>
+  <si>
+    <t>Full Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing </t>
+  </si>
+  <si>
+    <t>System Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debugging </t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Perform system testing (unit + integration testing)</t>
+  </si>
+  <si>
+    <t>Fix bugs and optimize IVR performance</t>
+  </si>
+  <si>
+    <t>Deploy IVR system to cloud platform (Render)</t>
+  </si>
+  <si>
+    <t>Validate deployed system and ensure end-to-end functionality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All modules  </t>
+  </si>
+  <si>
+    <t>Testing results</t>
+  </si>
+  <si>
+    <t>Backend + Frontend</t>
   </si>
 </sst>
 </file>
@@ -496,18 +589,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -887,7 +989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -1082,6 +1184,110 @@
         <v>22</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>166</v>
+      </c>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" t="s">
+        <v>152</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1089,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -1104,90 +1310,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
       <c r="I2" s="2">
         <v>41</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1199,29 +1405,29 @@
       <c r="C3" t="s">
         <v>51</v>
       </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>53</v>
+      <c r="D3" s="7">
+        <v>46054</v>
+      </c>
+      <c r="E3" s="7">
+        <v>46056</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
       </c>
       <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
         <v>54</v>
       </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>135</v>
+      <c r="J3" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -1229,37 +1435,37 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="D4" s="7">
+        <v>46057</v>
+      </c>
+      <c r="E4" s="7">
+        <v>46059</v>
       </c>
       <c r="F4" t="s">
         <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>135</v>
+        <v>58</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -1267,34 +1473,34 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="D5" s="7">
+        <v>46060</v>
+      </c>
+      <c r="E5" s="7">
+        <v>46062</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I5" t="s">
-        <v>56</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>135</v>
+        <v>54</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
@@ -1302,31 +1508,31 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>71</v>
+        <v>63</v>
+      </c>
+      <c r="D6" s="7">
+        <v>46063</v>
+      </c>
+      <c r="E6" s="7">
+        <v>46064</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>135</v>
+        <v>65</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -1334,40 +1540,40 @@
         <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" t="s">
-        <v>77</v>
+        <v>67</v>
+      </c>
+      <c r="D7" s="7">
+        <v>46065</v>
+      </c>
+      <c r="E7" s="7">
+        <v>46068</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I7" t="s">
-        <v>79</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>135</v>
+        <v>69</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -1375,38 +1581,213 @@
         <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>83</v>
+        <v>71</v>
+      </c>
+      <c r="D8" s="7">
+        <v>46069</v>
+      </c>
+      <c r="E8" s="7">
+        <v>46071</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>135</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="7">
+        <v>46073</v>
+      </c>
+      <c r="E9" s="7">
+        <v>46075</v>
+      </c>
+      <c r="F9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="9">
+        <v>5</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="7">
+        <v>46076</v>
+      </c>
+      <c r="E10" s="7">
+        <v>46078</v>
+      </c>
+      <c r="F10" t="s">
+        <v>153</v>
+      </c>
+      <c r="G10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="9">
+        <v>6</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" s="7">
+        <v>46079</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" t="s">
+        <v>157</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="9">
+        <v>5</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="7">
+        <v>46084</v>
+      </c>
+      <c r="E12" s="7">
+        <v>46086</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" t="s">
+        <v>158</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="9">
+        <v>5</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="7">
+        <v>46087</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46091</v>
+      </c>
+      <c r="F13" t="s">
+        <v>152</v>
+      </c>
+      <c r="G13" t="s">
+        <v>159</v>
+      </c>
+      <c r="H13" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="9">
+        <v>4</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1420,31 +1801,32 @@
     <mergeCell ref="F1:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
     <col min="3" max="3" width="37.42578125" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" customWidth="1"/>
+    <col min="4" max="4" width="51.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,13 +1834,13 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1466,13 +1848,13 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,13 +1862,13 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,13 +1876,55 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1510,46 +1934,46 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
     <col min="3" max="3" width="16.140625" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="30.85546875" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="38.85546875" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
     <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" customWidth="1"/>
+    <col min="9" max="9" width="35.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1559,26 +1983,26 @@
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" t="s">
-        <v>108</v>
+      <c r="C2" s="7">
+        <v>46054</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46058</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="H2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="I2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1588,26 +2012,26 @@
       <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" t="s">
-        <v>70</v>
+      <c r="C3" s="7">
+        <v>46059</v>
+      </c>
+      <c r="D3" s="7">
+        <v>46063</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1617,26 +2041,55 @@
       <c r="B4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
+      <c r="C4" s="7">
+        <v>46064</v>
+      </c>
+      <c r="D4" s="7">
+        <v>46068</v>
       </c>
       <c r="E4" t="s">
         <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="G4" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="H4" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="I4" t="s">
-        <v>122</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46073</v>
+      </c>
+      <c r="D5" s="7">
+        <v>46086</v>
+      </c>
+      <c r="E5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I5" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
